--- a/progset/Coverage scenarios_90%.xlsx
+++ b/progset/Coverage scenarios_90%.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tom.walsh\Documents\GitHub\cat-mnch\paper\progset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tom.walsh\Projects\A-coupled-model-analyses\progset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90BE5E9-EFF6-46E5-86E0-BFB39AE7B0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF726CA-3A69-4A99-A128-267A1DFCE4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7F4EF306-02DB-4B61-BDD2-954C1BFF99EB}"/>
+    <workbookView xWindow="13815" yWindow="-16680" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7F4EF306-02DB-4B61-BDD2-954C1BFF99EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Other" sheetId="1" r:id="rId1"/>
@@ -642,13 +642,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3AFC1AC-B068-4495-8860-D0B955869738}">
   <dimension ref="A1:AL35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="54.42578125" customWidth="1"/>
+    <col min="1" max="1" width="44.54296875" customWidth="1"/>
+    <col min="2" max="2" width="54.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -764,7 +764,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -880,7 +880,7 @@
         <v>0.75618640979999996</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -996,7 +996,7 @@
         <v>0.87844265100000007</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>0.58562843400000009</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>0.59006495940000014</v>
       </c>
     </row>
-    <row r="11" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>21</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>21</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>21</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>21</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>21</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>21</v>
       </c>
@@ -2776,7 +2776,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="19" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>21</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="20" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>31</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>0.75618640979999996</v>
       </c>
     </row>
-    <row r="21" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>31</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
         <v>31</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>31</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>0.90000000000000013</v>
       </c>
     </row>
-    <row r="24" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
         <v>31</v>
       </c>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
         <v>31</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>31</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>0.75618640979999996</v>
       </c>
     </row>
-    <row r="27" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>31</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>0.87844265100000007</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="29" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
         <v>23</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>23</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>23</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="32" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
         <v>23</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
         <v>23</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>23</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>23</v>
       </c>
@@ -4673,13 +4673,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{221B350A-2568-4FC3-99A0-A5B155596D16}">
   <dimension ref="A1:AL35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.140625" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="1" max="1" width="48.1796875" customWidth="1"/>
+    <col min="2" max="2" width="40.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -4911,7 +4911,7 @@
         <v>0.71516577059999986</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>0.87187977179999998</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -5476,7 +5476,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>0.58125318120000002</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>0.58850568780000001</v>
       </c>
     </row>
-    <row r="11" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>21</v>
       </c>
@@ -6066,7 +6066,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
@@ -6187,7 +6187,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>21</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>21</v>
       </c>
@@ -6429,7 +6429,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>21</v>
       </c>
@@ -6550,7 +6550,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>21</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>21</v>
       </c>
@@ -6792,7 +6792,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="19" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>21</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>31</v>
       </c>
@@ -7029,7 +7029,7 @@
         <v>0.71516577059999986</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>31</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
         <v>31</v>
       </c>
@@ -7189,7 +7189,7 @@
       <c r="AK22" s="10"/>
       <c r="AL22" s="10"/>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>31</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>0.90000000000000013</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
         <v>31</v>
       </c>
@@ -7421,7 +7421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
         <v>31</v>
       </c>
@@ -7537,7 +7537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>31</v>
       </c>
@@ -7653,7 +7653,7 @@
         <v>0.71516577059999986</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>31</v>
       </c>
@@ -7769,7 +7769,7 @@
         <v>0.87187977179999998</v>
       </c>
     </row>
-    <row r="28" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>23</v>
       </c>
@@ -7890,7 +7890,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="29" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
         <v>23</v>
       </c>
@@ -8006,7 +8006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
         <v>23</v>
       </c>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>23</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="32" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
         <v>23</v>
       </c>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
         <v>23</v>
       </c>
@@ -8475,7 +8475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>23</v>
       </c>
@@ -8596,7 +8596,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="35" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>23</v>
       </c>
@@ -8725,13 +8725,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBEB2D7F-7C57-4F43-896C-F1EF4D0F649A}">
   <dimension ref="A1:AL35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" customWidth="1"/>
-    <col min="2" max="2" width="56.28515625" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" customWidth="1"/>
+    <col min="2" max="2" width="56.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>0.58009926059999994</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -9079,7 +9079,7 @@
         <v>0.842378301</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -9195,7 +9195,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -9311,7 +9311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -9427,7 +9427,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -9543,7 +9543,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -9659,7 +9659,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -9775,7 +9775,7 @@
         <v>0.58562843400000009</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -9891,7 +9891,7 @@
         <v>0.57163269359999991</v>
       </c>
     </row>
-    <row r="11" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
@@ -10012,7 +10012,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>21</v>
       </c>
@@ -10133,7 +10133,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
@@ -10254,7 +10254,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>21</v>
       </c>
@@ -10375,7 +10375,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>21</v>
       </c>
@@ -10496,7 +10496,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>21</v>
       </c>
@@ -10617,7 +10617,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>21</v>
       </c>
@@ -10738,7 +10738,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>21</v>
       </c>
@@ -10859,7 +10859,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="19" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>21</v>
       </c>
@@ -10980,7 +10980,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="20" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>31</v>
       </c>
@@ -11096,7 +11096,7 @@
         <v>0.58009926059999994</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>31</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
         <v>31</v>
       </c>
@@ -11328,7 +11328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>31</v>
       </c>
@@ -11444,7 +11444,7 @@
         <v>0.90000000000000013</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
         <v>31</v>
       </c>
@@ -11560,7 +11560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
         <v>31</v>
       </c>
@@ -11676,7 +11676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>31</v>
       </c>
@@ -11792,7 +11792,7 @@
         <v>0.58009926059999994</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>31</v>
       </c>
@@ -11908,7 +11908,7 @@
         <v>0.842378301</v>
       </c>
     </row>
-    <row r="28" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>23</v>
       </c>
@@ -12029,7 +12029,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
         <v>23</v>
       </c>
@@ -12145,7 +12145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
         <v>23</v>
       </c>
@@ -12261,7 +12261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>23</v>
       </c>
@@ -12382,7 +12382,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
         <v>23</v>
       </c>
@@ -12498,7 +12498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
         <v>23</v>
       </c>
@@ -12614,7 +12614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>23</v>
       </c>
@@ -12735,7 +12735,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="35" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>23</v>
       </c>
@@ -12863,6 +12863,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a222eb7ab0cf4508cce7c7319f3c2955">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" xmlns:ns3="d27fc6f8-d518-4cdb-8bab-875cbacf3583" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="daa2ef1fbb8a42edff9ae6aeec006a1a" ns2:_="" ns3:_="">
     <xsd:import namespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
@@ -13079,33 +13098,39 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B05BD7D-A414-4482-AB60-C85316338E7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35C08B1C-721B-4C8C-9EA6-F414DD238EC0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80057CC5-2ED2-4BFE-AF5E-C745CA65ECF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80057CC5-2ED2-4BFE-AF5E-C745CA65ECF8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35C08B1C-721B-4C8C-9EA6-F414DD238EC0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B05BD7D-A414-4482-AB60-C85316338E7C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
+    <ds:schemaRef ds:uri="d27fc6f8-d518-4cdb-8bab-875cbacf3583"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>